--- a/base_prov/ml/ml_abbott_2026-08-10.xlsx
+++ b/base_prov/ml/ml_abbott_2026-08-10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\como se me cante\retail-chatbot-main\eci_abbott-main\base_prov\ml\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856CEF75-5B9B-4DB4-82AC-44A91A970281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD4E2D9-A84B-4DE9-B965-F2EBFA12DDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$80</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="165">
   <si>
     <t>fecha</t>
   </si>
@@ -164,9 +164,6 @@
     <t>FÓRMULA INFANTIL CON HIERRO SIMILAC ETAPA 1 350 GRAMOS N/A</t>
   </si>
   <si>
-    <t>LECHE SIMILAC ARROZ - ADVANCE 0 A 12 MESES LATA 400 G ARROZ</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -197,9 +194,6 @@
     <t>PACK X24 ENSURE CLÁSICO CHOCOLATE BEBIDA, VITAMINAS CHOCOLATE</t>
   </si>
   <si>
-    <t>PEDIASURE LÍQUIDO PACK 16 PIEZAS 237ML FRESA FRESA</t>
-  </si>
-  <si>
     <t>PEDIALYTE 12 PACK SABOR CEREZA 30 MEQ</t>
   </si>
   <si>
@@ -308,42 +302,27 @@
     <t>https://www.mercadolibre.com.mx/pack-x12-sabor-fresa-45-meq-pedialyte/p/MLM53151422#polycard_client=search-desktop&amp;be_origin=backend&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=8922b367-1b75-4ce0-a725-213ffd3df031&amp;wid=MLM3857885868&amp;sid=search</t>
   </si>
   <si>
-    <t>https://www.mercadolibre.com.mx/pedialyte-12-pack-sabor-uva-60-meq/p/MLM61340869?pdp_filters=item_id:MLM2861827737#is_advertising=true&amp;searchVariation=MLM61340869&amp;backend_model=search-backend&amp;be_origin=backend&amp;position=5&amp;search_layout=grid&amp;type=pad&amp;tracking_id=5a7d5bd7-83ba-4711-8e96-45b6e7584169&amp;ad_domain=VQCATCORE_LST&amp;ad_position=5&amp;ad_click_id=MDgxZDgzNzMtZTM3Yi00MzFkLThjMGYtZjY1MDE4NDZkYzlj</t>
-  </si>
-  <si>
     <t>https://www.mercadolibre.com.mx/pack-x12-pedialyte-sabor-fresa-500ml/p/MLM53178714?pdp_filters=item_id:MLM2385333737#is_advertising=true&amp;searchVariation=MLM53178714&amp;backend_model=search-backend&amp;be_origin=backend&amp;position=2&amp;search_layout=grid&amp;type=pad&amp;tracking_id=26ee9276-0f48-4770-add9-a78dc1b80d3b&amp;ad_domain=VQCATCORE_LST&amp;ad_position=2&amp;ad_click_id=YTJjOWExNmMtNzY2NC00OGYxLTk3ZjktMThkODE5YWJlMzc0</t>
   </si>
   <si>
     <t>https://www.mercadolibre.com.mx/pedialyte-12-pack-sabor-coco-30-meq/p/MLM67737065?pdp_filters=item_id:MLM5164338894#is_advertising=true&amp;searchVariation=MLM67737065&amp;backend_model=search-backend&amp;be_origin=backend&amp;position=19&amp;search_layout=grid&amp;type=pad&amp;tracking_id=91ad6538-5cb7-4051-afff-8f1c455b883c&amp;ad_domain=VQCATCORE_LST&amp;ad_position=19&amp;ad_click_id=MWU2OWU1ZjMtODgzMy00ZWEzLTljNTQtOWM4ZDg0ZmUyMzA1</t>
   </si>
   <si>
-    <t>https://www.mercadolibre.com.mx/formula-infantil-abbott-similac-3-con-hmo-de-800g/up/MLMU924030848?pdp_filters=shipping%3Afulfillment%7Cdeal%3AMLM1020488-1#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=33920ee2-4335-479d-98d3-5cee5c0bff4a&amp;wid=MLM1918678287&amp;sid=search</t>
-  </si>
-  <si>
     <t>PACK X24 PIEZAS ALIMENTACIÓN ESPECIALIZADA VAINILLA 237 ML C/U PULMOCARE</t>
   </si>
   <si>
     <t>https://www.mercadolibre.com.mx/pack-x24-piezas-alimentacion-especializada-vainilla-237-ml-cu-pulmocare/p/MLM35656419?pdp_filters=shipping%3Afulfillment%7Cdeal%3AMLM1020488-1#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=6b2216e9-81cb-4b72-bfae-2819db6efb6b&amp;wid=MLM2049662131&amp;sid=search</t>
   </si>
   <si>
-    <t>https://www.mercadolibre.com.mx/pack-x24-ensure-237ml-sabor-fresa/p/MLM46915695?pdp_filters=shipping%3Afulfillment%7Cdeal%3AMLM1020488-1#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=33151122-2530-4474-9207-e1602d3438a0&amp;wid=MLM3588024756&amp;sid=search</t>
-  </si>
-  <si>
     <t>PACK X24 ENSURE CLÁSICO VAINILLA, BEBIDA, VITAMINAS</t>
   </si>
   <si>
     <t>PACK X24 ENSURE 237ML SABOR FRESA</t>
   </si>
   <si>
-    <t>https://www.mercadolibre.com.mx/pack-x24-ensure-clasico-vainilla-bebida-vitaminas/p/MLM47074835?pdp_filters=deal%3AMLM1020488-1%7Cshipping%3Afulfillment#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=e085b9aa-87fd-4988-9a32-0562750c808b&amp;wid=MLM2258045645&amp;sid=search</t>
-  </si>
-  <si>
     <t>PACK X24 GLUCERNA VAINILA BEBIDA, SIN AZÚCAR, VITAMINAS</t>
   </si>
   <si>
-    <t>https://www.mercadolibre.com.mx/pack-x24-glucerna-vainila-bebida-sin-azucar-vitaminas/up/MLMU904428808?pdp_filters=shipping%3Afulfillment%7Cdeal%3AMLM1020488-1#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=69c0b18f-8408-428a-bd15-37018d8b7818&amp;wid=MLM1599499235&amp;sid=search</t>
-  </si>
-  <si>
     <t>PACK X24 BEBIDA SIN AZÚCAR VITAMINAS FRESA 5.69KG GLUCERNA</t>
   </si>
   <si>
@@ -374,21 +353,12 @@
     <t>PACK X24 FRESA BEBIDA, VITAMINAS Y MINERALES PEDIASURE</t>
   </si>
   <si>
-    <t>https://www.mercadolibre.com.mx/pack-x24-fresa-bebida-vitaminas-y-minerales-pediasure/up/MLMU2972735360?pdp_filters=shipping%3Afulfillment%7Cdeal%3AMLM1020488-1#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=6&amp;type=product&amp;tracking_id=5cd186e0-3552-4fd2-b30d-b1b2cbeb37bf&amp;wid=MLM3537826888&amp;sid=search</t>
-  </si>
-  <si>
     <t>PEDIASURE ALIMENTACIÓN ESPECIALIZADA VAINILLA EN POLVO 400G</t>
   </si>
   <si>
-    <t>https://www.mercadolibre.com.mx/pediasure-alimentacion-especializada-vainilla-en-polvo-400g/up/MLMU445110100?pdp_filters=shipping%3Afulfillment%7Cdeal%3AMLM1020488-1#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=eca21e1f-e9f3-4224-9cc0-db1b4582c8d5&amp;wid=MLM1344836181&amp;sid=search</t>
-  </si>
-  <si>
     <t>PEDIASURE ALIMENTACIÓN ESPECIALIZADA FRESA EN POLVO 400G</t>
   </si>
   <si>
-    <t>https://www.mercadolibre.com.mx/pediasure-alimentacion-especializada-fresa-en-polvo-400g/up/MLMU897063446?pdp_filters=shipping%3Afulfillment%7Cdeal%3AMLM1020488-1#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=5&amp;type=product&amp;tracking_id=a6f18cfe-72de-4249-8c9c-91c52f02f662&amp;wid=MLM1485178537&amp;sid=search</t>
-  </si>
-  <si>
     <t>FÓRMULA PARA ALIMENTACIÓN ENSURE ADVANCE CHOCOLATE 400G</t>
   </si>
   <si>
@@ -404,9 +374,6 @@
     <t>https://www.mercadolibre.com.mx/pack-x30-suplemento-nutricional-vainilla-220mlcu-prosure/p/MLM48603312?pdp_filters=shipping%3Afulfillment%7Cdeal%3AMLM1020488-1#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=2&amp;type=product&amp;tracking_id=6df53103-7934-4e0a-8e55-0fabe499d582&amp;wid=MLM2285029147&amp;sid=search</t>
   </si>
   <si>
-    <t>https://www.mercadolibre.com.mx/similac-etapa-3-1800-g-formula-infantil-de-continuacion/up/MLMU939843204?pdp_filters=deal%3AMLM1020488-1%7Cshipping%3Afulfillment#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=3&amp;type=product&amp;tracking_id=916a686c-aa0b-4854-9ed5-ed05cf9590b1&amp;wid=MLM2035768243&amp;sid=search</t>
-  </si>
-  <si>
     <t>SIMILAC AR FÓRMULA CON HIERRO A BASE DE ALMIDÓN DE ARROZ 0 A 12 MESES 350G</t>
   </si>
   <si>
@@ -431,9 +398,6 @@
     <t>SIMILAC TOTAL CONFORT ETAPA 2 FÓRMULA DE CONTINUACIÓN PARA NIÑOS CON NECESIDADES ESPECIALES DE NUTRICIÓN 800G</t>
   </si>
   <si>
-    <t>DISTRIBUIDORA PEKOLINES</t>
-  </si>
-  <si>
     <t>SIMILAC TOTAL COMFORT ETAPA 1 FÓRMULA PARA LACTANTES DE 0-12 MESES CON NECESIDADES ESPECIALES DE NUTRICIÓN 350G</t>
   </si>
   <si>
@@ -443,9 +407,6 @@
     <t>FÓRMULA INFANTIL LECHE EN POLVO TOTAL COMFORT 800 GR SIMILAC</t>
   </si>
   <si>
-    <t>https://www.mercadolibre.com.mx/formula-infantil-leche-en-polvo-total-comfort-800-gr-similac/up/MLMU3077128838?pdp_filters=shipping%3Afulfillment%7Cdeal%3AMLM1020488-1#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=5&amp;type=product&amp;tracking_id=6d15abb3-d5f8-4377-bd70-f5badc7003fe&amp;wid=MLM2261442019&amp;sid=search</t>
-  </si>
-  <si>
     <t>PACK X2 SIMILAC TOTAL COMFORT 1 800G C/U</t>
   </si>
   <si>
@@ -455,9 +416,6 @@
     <t>PEDIASURE LÍQUIDO PACK 16 PIEZAS 237 ML VAINILLA</t>
   </si>
   <si>
-    <t>https://www.mercadolibre.com.mx/pediasure-liquido-pack-16-piezas-237-ml-vainilla/up/MLMU3887163171?pdp_filters=shipping%3Afulfillment%7Cdeal%3AMLM1020488-1#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=7&amp;type=product&amp;tracking_id=218b7748-d546-4199-a1bf-febf3d29ba53&amp;wid=MLM2853082095&amp;sid=search</t>
-  </si>
-  <si>
     <t>https://www.mercadolibre.com.mx/pediasure-liquido-pack-16-piezas-237ml-fresa/p/MLM69626024?pdp_filters=shipping%3Afulfillment%7Cdeal%3AMLM1020488-1#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=4&amp;type=product&amp;tracking_id=6997a165-5eb2-4362-ba50-692a0187e98d&amp;wid=MLM5336513374&amp;sid=search</t>
   </si>
   <si>
@@ -467,9 +425,6 @@
     <t>https://www.mercadolibre.com.mx/leche-similac-neosure-bebes-con-bajo-peso-0-a-12-meses-370g/up/MLMU874834097?pdp_filters=item_id:MLM1386166955#intervention_type=MARKET&amp;position=1&amp;search_layout=grid&amp;type=cart_intervention&amp;tracking_id=682a3341-fd7f-41ac-816d-13e8c153eff4</t>
   </si>
   <si>
-    <t>PEDIASURE POLVO 10+ 400G CHOCOLATE</t>
-  </si>
-  <si>
     <t>SIMILAC ETAPA 3 1800 G, FÓRMULA INFANTIL DE CONTINUACIÓN</t>
   </si>
   <si>
@@ -521,12 +476,6 @@
     <t>https://www.mercadolibre.com.mx/suplemento-alimenticio-ensure-en-polvo-sabor-chocolate-400g/p/MLM18564595</t>
   </si>
   <si>
-    <t>https://www.mercadolibre.com.mx/suplemento-en-polvo-ensure-sabor-vainilla-en-lata-de-400g/p/MLM18564592</t>
-  </si>
-  <si>
-    <t>https://www.mercadolibre.com.mx/pack-x16-suplemento-nutricional-advance-hmb-3792-ml-ensure-cafe/p/MLM45641341</t>
-  </si>
-  <si>
     <t>https://www.mercadolibre.com.mx/ensure-procare-vitaminasmultivitaminicosminerales-nutricional-liquido-hmb-whey-protein-pack-30-unidades-220ml-vainilla/p/MLM53303424</t>
   </si>
   <si>
@@ -537,15 +486,57 @@
   </si>
   <si>
     <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>NUTRIO</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/pack-x16-ensure-advance-fresa-bebida-con-hmb/p/MLM41704978#polycard_client=search-desktop&amp;float_highlight=last_units&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=0f1c1e3a-4b0f-4da5-a194-b2816e8aea13&amp;wid=MLM2883922583&amp;sid=search</t>
+  </si>
+  <si>
+    <t>LECHE SIMILAC ARROZ - ADVANCE 0 A 12 MESES LATA 400 G</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/leche-similac-arroz--advance-0-a-12-meses-lata-400-g/up/MLMU893569081#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=2&amp;type=product&amp;tracking_id=ab2d8c6a-56c2-4302-9a5a-6b19d445fe27&amp;wid=MLM1485136166&amp;sid=search</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/pack-x24-ensure-clasico-vainilla-bebida-vitaminas/up/MLMU2972736800?pdp_filters=item_id:MLM3537751314#intervention_type=MARKET&amp;position=5&amp;search_layout=grid&amp;type=cart_intervention&amp;tracking_id=7a3df41c-93a6-43b0-a5bb-c0ea20b62eca</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/pack-x24-ensure-237ml-sabor-fresa/up/MLMU904426900?pdp_filters=item_id:MLM1599152042#intervention_type=MARKET&amp;position=5&amp;search_layout=grid&amp;type=cart_intervention&amp;tracking_id=65691e22-4bd7-4e86-83f5-829a27391701</t>
+  </si>
+  <si>
+    <t>ECSOINN10</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/pediasure-liquido-pack-16-piezas-237-ml-vainilla/p/MLM69698928?pdp_filters=item_id:MLM5583168228#is_advertising=true&amp;searchVariation=MLM69698928&amp;backend_model=search-backend&amp;be_origin=backend&amp;position=3&amp;search_layout=grid&amp;type=pad&amp;tracking_id=c59b604f-d77d-40d8-85a0-6ea7f3e61bf7&amp;ad_domain=VQCATCORE_LST&amp;ad_position=3&amp;ad_click_id=MTg0NmVlOWYtMjg4ZS00MDc3LWEzN2ItMWE1OTIzYjg3MmIw</t>
+  </si>
+  <si>
+    <t>PEDIASURE LÍQUIDO PACK 16 PIEZAS 237ML FRESA</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/pedialyte-12-pack-sabor-manzana-30-meq/p/MLM75766166#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=5d02909a-4f27-48bd-b930-d80a118b5e26&amp;wid=MLM3194955475&amp;sid=search</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/suplemento-en-polvo-sabor-a-fresa-lata-400g-clasico-ensure/up/MLMU4188275451#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=2&amp;type=product&amp;tracking_id=6ea04ecd-68c5-42ee-a8ce-01271eba158c&amp;wid=MLM3071870879&amp;sid=search</t>
+  </si>
+  <si>
+    <t>PEDIASURE POLVO 10+ 400G CHOCOLATE CHOCOLATE</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/pedialyte-sabor-pepino-limon-12-pack-30-meq/p/MLM68668993?pdp_filters=item_id:MLM5286208692#is_advertising=true&amp;searchVariation=MLM68668993&amp;backend_model=search-backend&amp;be_origin=backend&amp;position=2&amp;search_layout=grid&amp;type=pad&amp;tracking_id=f2dc80dc-e843-4457-8a9c-b9247d42693d&amp;ad_domain=VQCATCORE_LST&amp;ad_position=2&amp;ad_click_id=ZjExNGVmMzEtMWNiOS00ODdjLTlkNTUtODczMDI2NzNlNjVk</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/pedialyte-sabor-pina-naranja-12-pack-30-meq/p/MLM67728273#polycard_client=search-desktop&amp;be_origin=backend&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=1bb15e74-76f8-4ad8-959d-e6d1b9f3c8b9&amp;wid=MLM5158476730&amp;sid=search</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -601,12 +592,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -927,7 +917,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -937,10 +927,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -952,22 +942,22 @@
         <v>5</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>6</v>
@@ -975,7 +965,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -987,7 +977,7 @@
         <v>1344818213</v>
       </c>
       <c r="E2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
@@ -1014,7 +1004,7 @@
         <v>362</v>
       </c>
       <c r="N2" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="O2" t="s">
         <v>9</v>
@@ -1022,7 +1012,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -1034,10 +1024,10 @@
         <v>2251566859</v>
       </c>
       <c r="E3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F3" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="G3">
         <v>1000</v>
@@ -1046,7 +1036,7 @@
         <v>10</v>
       </c>
       <c r="I3">
-        <v>900</v>
+        <v>916</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -1061,7 +1051,7 @@
         <v>1227</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="O3" t="s">
         <v>11</v>
@@ -1069,7 +1059,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -1081,7 +1071,7 @@
         <v>3537789846</v>
       </c>
       <c r="E4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F4" t="s">
         <v>7</v>
@@ -1093,7 +1083,7 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -1108,7 +1098,7 @@
         <v>1077</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="O4" t="s">
         <v>9</v>
@@ -1116,7 +1106,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -1128,19 +1118,19 @@
         <v>1344811825</v>
       </c>
       <c r="E5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G5">
         <v>10000</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>2333</v>
+        <v>42</v>
+      </c>
+      <c r="I5" t="s">
+        <v>42</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1155,7 +1145,7 @@
         <v>521</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="O5" t="s">
         <v>11</v>
@@ -1163,7 +1153,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -1175,7 +1165,7 @@
         <v>53398238</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F6" t="s">
         <v>7</v>
@@ -1187,7 +1177,7 @@
         <v>12</v>
       </c>
       <c r="I6">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J6">
         <v>7</v>
@@ -1202,7 +1192,7 @@
         <v>895</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="O6" t="s">
         <v>9</v>
@@ -1210,7 +1200,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -1222,7 +1212,7 @@
         <v>2372456637</v>
       </c>
       <c r="E7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F7" t="s">
         <v>7</v>
@@ -1234,7 +1224,7 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="J7">
         <v>7</v>
@@ -1249,7 +1239,7 @@
         <v>742</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="O7" t="s">
         <v>9</v>
@@ -1257,7 +1247,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -1269,7 +1259,7 @@
         <v>5336510898</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F8" t="s">
         <v>7</v>
@@ -1296,7 +1286,7 @@
         <v>807</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="O8" t="s">
         <v>9</v>
@@ -1304,7 +1294,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -1316,7 +1306,7 @@
         <v>5336952032</v>
       </c>
       <c r="E9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F9" t="s">
         <v>7</v>
@@ -1328,7 +1318,7 @@
         <v>12</v>
       </c>
       <c r="I9">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1343,7 +1333,7 @@
         <v>1182</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="O9" t="s">
         <v>9</v>
@@ -1351,7 +1341,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -1363,7 +1353,7 @@
         <v>5336510580</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F10" t="s">
         <v>7</v>
@@ -1390,7 +1380,7 @@
         <v>756</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="O10" t="s">
         <v>9</v>
@@ -1398,7 +1388,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -1410,7 +1400,7 @@
         <v>5336510588</v>
       </c>
       <c r="E11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F11" t="s">
         <v>7</v>
@@ -1422,7 +1412,7 @@
         <v>12</v>
       </c>
       <c r="I11">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1437,7 +1427,7 @@
         <v>715</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="O11" t="s">
         <v>9</v>
@@ -1445,7 +1435,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -1457,7 +1447,7 @@
         <v>2372468319</v>
       </c>
       <c r="E12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F12" t="s">
         <v>7</v>
@@ -1469,7 +1459,7 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="J12">
         <v>9</v>
@@ -1484,7 +1474,7 @@
         <v>944</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="O12" t="s">
         <v>9</v>
@@ -1492,7 +1482,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -1504,7 +1494,7 @@
         <v>2853082117</v>
       </c>
       <c r="E13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F13" t="s">
         <v>7</v>
@@ -1531,7 +1521,7 @@
         <v>805</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="O13" t="s">
         <v>9</v>
@@ -1539,7 +1529,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -1551,7 +1541,7 @@
         <v>1973439527</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F14" t="s">
         <v>7</v>
@@ -1563,7 +1553,7 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>13045</v>
+        <v>14866</v>
       </c>
       <c r="J14">
         <v>6</v>
@@ -1578,7 +1568,7 @@
         <v>792</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="O14" t="s">
         <v>9</v>
@@ -1586,7 +1576,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -1598,10 +1588,10 @@
         <v>2268089725</v>
       </c>
       <c r="E15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F15" t="s">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G15">
         <v>1000</v>
@@ -1610,7 +1600,7 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>1226</v>
+        <v>1255</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -1625,7 +1615,7 @@
         <v>1147</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="O15" t="s">
         <v>11</v>
@@ -1633,7 +1623,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -1645,34 +1635,34 @@
         <v>3537789844</v>
       </c>
       <c r="E16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F16" t="s">
-        <v>43</v>
-      </c>
-      <c r="G16" t="s">
-        <v>43</v>
+        <v>150</v>
+      </c>
+      <c r="G16">
+        <v>1000</v>
       </c>
       <c r="H16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16" t="s">
-        <v>43</v>
-      </c>
-      <c r="J16" t="s">
-        <v>43</v>
-      </c>
-      <c r="K16" t="s">
-        <v>43</v>
-      </c>
-      <c r="L16" t="s">
-        <v>43</v>
-      </c>
-      <c r="M16" t="s">
-        <v>43</v>
+        <v>10</v>
+      </c>
+      <c r="I16">
+        <v>264</v>
+      </c>
+      <c r="J16">
+        <v>4</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>46</v>
+      </c>
+      <c r="M16">
+        <v>528</v>
       </c>
       <c r="N16" t="s">
-        <v>43</v>
+        <v>151</v>
       </c>
       <c r="O16" t="s">
         <v>11</v>
@@ -1680,7 +1670,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -1692,22 +1682,22 @@
         <v>1487393123</v>
       </c>
       <c r="E17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F17" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="G17">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="H17" t="s">
-        <v>10</v>
-      </c>
-      <c r="I17">
-        <v>17897</v>
+        <v>42</v>
+      </c>
+      <c r="I17" t="s">
+        <v>42</v>
       </c>
       <c r="J17">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -1719,15 +1709,15 @@
         <v>479</v>
       </c>
       <c r="N17" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="O17" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -1739,42 +1729,42 @@
         <v>1487412130</v>
       </c>
       <c r="E18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F18" t="s">
-        <v>7</v>
-      </c>
-      <c r="G18">
-        <v>5000</v>
+        <v>42</v>
+      </c>
+      <c r="G18" t="s">
+        <v>42</v>
       </c>
       <c r="H18" t="s">
-        <v>10</v>
-      </c>
-      <c r="I18">
-        <v>17897</v>
-      </c>
-      <c r="J18">
-        <v>12</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>57</v>
-      </c>
-      <c r="M18">
-        <v>531</v>
+        <v>42</v>
+      </c>
+      <c r="I18" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" t="s">
+        <v>42</v>
+      </c>
+      <c r="K18" t="s">
+        <v>42</v>
+      </c>
+      <c r="L18" t="s">
+        <v>42</v>
+      </c>
+      <c r="M18" t="s">
+        <v>42</v>
       </c>
       <c r="N18" t="s">
-        <v>161</v>
+        <v>42</v>
       </c>
       <c r="O18" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -1786,42 +1776,42 @@
         <v>3537776704</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G19">
-        <v>1000</v>
+        <v>42</v>
+      </c>
+      <c r="G19" t="s">
+        <v>42</v>
       </c>
       <c r="H19" t="s">
-        <v>10</v>
-      </c>
-      <c r="I19">
-        <v>1226</v>
-      </c>
-      <c r="J19">
-        <v>6</v>
-      </c>
-      <c r="K19">
-        <v>1</v>
-      </c>
-      <c r="L19">
-        <v>63</v>
-      </c>
-      <c r="M19">
-        <v>1109</v>
+        <v>42</v>
+      </c>
+      <c r="I19" t="s">
+        <v>42</v>
+      </c>
+      <c r="J19" t="s">
+        <v>42</v>
+      </c>
+      <c r="K19" t="s">
+        <v>42</v>
+      </c>
+      <c r="L19" t="s">
+        <v>42</v>
+      </c>
+      <c r="M19" t="s">
+        <v>42</v>
       </c>
       <c r="N19" t="s">
-        <v>162</v>
+        <v>42</v>
       </c>
       <c r="O19" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -1833,7 +1823,7 @@
         <v>3880978850</v>
       </c>
       <c r="E20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F20" t="s">
         <v>7</v>
@@ -1860,7 +1850,7 @@
         <v>1008</v>
       </c>
       <c r="N20" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="O20" t="s">
         <v>9</v>
@@ -1868,7 +1858,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -1880,7 +1870,7 @@
         <v>3866576502</v>
       </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F21" t="s">
         <v>7</v>
@@ -1889,10 +1879,10 @@
         <v>1000</v>
       </c>
       <c r="H21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J21">
         <v>3</v>
@@ -1907,7 +1897,7 @@
         <v>1166</v>
       </c>
       <c r="N21" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="O21" t="s">
         <v>9</v>
@@ -1915,7 +1905,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -1927,7 +1917,7 @@
         <v>2975827632</v>
       </c>
       <c r="E22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F22" t="s">
         <v>7</v>
@@ -1954,7 +1944,7 @@
         <v>783</v>
       </c>
       <c r="N22" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="O22" t="s">
         <v>9</v>
@@ -1962,7 +1952,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -1974,34 +1964,34 @@
         <v>1387013248</v>
       </c>
       <c r="E23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O23" t="s">
         <v>11</v>
@@ -2009,7 +1999,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -2021,34 +2011,34 @@
         <v>3833162316</v>
       </c>
       <c r="E24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O24" t="s">
         <v>11</v>
@@ -2056,7 +2046,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -2068,34 +2058,34 @@
         <v>3537751334</v>
       </c>
       <c r="E25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O25" t="s">
         <v>11</v>
@@ -2103,7 +2093,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -2115,42 +2105,42 @@
         <v>1918678287</v>
       </c>
       <c r="E26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F26" t="s">
-        <v>7</v>
-      </c>
-      <c r="G26">
-        <v>1000</v>
+        <v>42</v>
+      </c>
+      <c r="G26" t="s">
+        <v>42</v>
       </c>
       <c r="H26" t="s">
-        <v>10</v>
-      </c>
-      <c r="I26">
-        <v>18</v>
-      </c>
-      <c r="J26">
-        <v>3</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>49</v>
-      </c>
-      <c r="M26">
-        <v>733</v>
+        <v>42</v>
+      </c>
+      <c r="I26" t="s">
+        <v>42</v>
+      </c>
+      <c r="J26" t="s">
+        <v>42</v>
+      </c>
+      <c r="K26" t="s">
+        <v>42</v>
+      </c>
+      <c r="L26" t="s">
+        <v>42</v>
+      </c>
+      <c r="M26" t="s">
+        <v>42</v>
       </c>
       <c r="N26" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="O26" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -2162,34 +2152,34 @@
         <v>1344793647</v>
       </c>
       <c r="E27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O27" t="s">
         <v>11</v>
@@ -2197,7 +2187,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -2209,34 +2199,34 @@
         <v>1344811832</v>
       </c>
       <c r="E28" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O28" t="s">
         <v>11</v>
@@ -2244,7 +2234,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -2256,7 +2246,7 @@
         <v>2334097590</v>
       </c>
       <c r="E29" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F29" t="s">
         <v>7</v>
@@ -2268,7 +2258,7 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>926</v>
+        <v>945</v>
       </c>
       <c r="J29">
         <v>2</v>
@@ -2283,7 +2273,7 @@
         <v>606</v>
       </c>
       <c r="N29" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="O29" t="s">
         <v>9</v>
@@ -2291,66 +2281,66 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>152</v>
       </c>
       <c r="D30">
         <v>1485136166</v>
       </c>
       <c r="E30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F30" t="s">
-        <v>43</v>
-      </c>
-      <c r="G30" t="s">
-        <v>43</v>
+        <v>7</v>
+      </c>
+      <c r="G30">
+        <v>5</v>
       </c>
       <c r="H30" t="s">
-        <v>43</v>
-      </c>
-      <c r="I30" t="s">
-        <v>43</v>
-      </c>
-      <c r="J30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K30" t="s">
-        <v>43</v>
-      </c>
-      <c r="L30" t="s">
-        <v>43</v>
-      </c>
-      <c r="M30" t="s">
-        <v>43</v>
+        <v>153</v>
+      </c>
+      <c r="I30">
+        <v>11</v>
+      </c>
+      <c r="J30">
+        <v>5</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>53</v>
+      </c>
+      <c r="M30">
+        <v>470</v>
       </c>
       <c r="N30" t="s">
-        <v>43</v>
+        <v>154</v>
       </c>
       <c r="O30" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D31">
         <v>2975802702</v>
       </c>
       <c r="E31" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F31" t="s">
         <v>7</v>
@@ -2362,7 +2352,7 @@
         <v>8</v>
       </c>
       <c r="I31">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J31">
         <v>8</v>
@@ -2377,7 +2367,7 @@
         <v>1356</v>
       </c>
       <c r="N31" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="O31" t="s">
         <v>9</v>
@@ -2385,46 +2375,46 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D32">
         <v>2042277005</v>
       </c>
       <c r="E32" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O32" t="s">
         <v>11</v>
@@ -2432,46 +2422,46 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D33">
         <v>3537852808</v>
       </c>
       <c r="E33" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O33" t="s">
         <v>11</v>
@@ -2479,19 +2469,19 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D34">
         <v>1599152042</v>
       </c>
       <c r="E34" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F34" t="s">
         <v>7</v>
@@ -2500,16 +2490,16 @@
         <v>5000</v>
       </c>
       <c r="H34" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I34">
-        <v>1436</v>
+        <v>40</v>
       </c>
       <c r="J34">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34">
         <v>33</v>
@@ -2518,7 +2508,7 @@
         <v>1080</v>
       </c>
       <c r="N34" t="s">
-        <v>96</v>
+        <v>156</v>
       </c>
       <c r="O34" t="s">
         <v>9</v>
@@ -2526,19 +2516,19 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D35">
         <v>3537751314</v>
       </c>
       <c r="E35" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F35" t="s">
         <v>7</v>
@@ -2547,16 +2537,16 @@
         <v>5000</v>
       </c>
       <c r="H35" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I35">
-        <v>1436</v>
+        <v>5</v>
       </c>
       <c r="J35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35">
         <v>51</v>
@@ -2565,7 +2555,7 @@
         <v>669</v>
       </c>
       <c r="N35" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="O35" t="s">
         <v>9</v>
@@ -2573,66 +2563,66 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D36">
         <v>1599499235</v>
       </c>
       <c r="E36" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F36" t="s">
-        <v>7</v>
-      </c>
-      <c r="G36">
-        <v>1000</v>
+        <v>42</v>
+      </c>
+      <c r="G36" t="s">
+        <v>42</v>
       </c>
       <c r="H36" t="s">
-        <v>10</v>
-      </c>
-      <c r="I36">
-        <v>26</v>
-      </c>
-      <c r="J36">
-        <v>6</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>55</v>
-      </c>
-      <c r="M36">
-        <v>336</v>
+        <v>42</v>
+      </c>
+      <c r="I36" t="s">
+        <v>42</v>
+      </c>
+      <c r="J36" t="s">
+        <v>42</v>
+      </c>
+      <c r="K36" t="s">
+        <v>42</v>
+      </c>
+      <c r="L36" t="s">
+        <v>42</v>
+      </c>
+      <c r="M36" t="s">
+        <v>42</v>
       </c>
       <c r="N36" t="s">
-        <v>101</v>
+        <v>42</v>
       </c>
       <c r="O36" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D37">
         <v>3537826884</v>
       </c>
       <c r="E37" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F37" t="s">
         <v>7</v>
@@ -2644,7 +2634,7 @@
         <v>10</v>
       </c>
       <c r="I37">
-        <v>893</v>
+        <v>911</v>
       </c>
       <c r="J37">
         <v>4</v>
@@ -2659,7 +2649,7 @@
         <v>1323</v>
       </c>
       <c r="N37" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="O37" t="s">
         <v>9</v>
@@ -2667,31 +2657,31 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="D38">
         <v>2853082095</v>
       </c>
       <c r="E38" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F38" t="s">
-        <v>7</v>
+        <v>157</v>
       </c>
       <c r="G38">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="H38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -2706,7 +2696,7 @@
         <v>1323</v>
       </c>
       <c r="N38" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="O38" t="s">
         <v>9</v>
@@ -2714,19 +2704,19 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="D39">
         <v>2853082131</v>
       </c>
       <c r="E39" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F39" t="s">
         <v>7</v>
@@ -2753,7 +2743,7 @@
         <v>1549</v>
       </c>
       <c r="N39" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="O39" t="s">
         <v>9</v>
@@ -2761,46 +2751,46 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D40">
         <v>5078833892</v>
       </c>
       <c r="E40" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O40" t="s">
         <v>11</v>
@@ -2808,19 +2798,19 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D41">
         <v>3857885868</v>
       </c>
       <c r="E41" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F41" t="s">
         <v>7</v>
@@ -2847,7 +2837,7 @@
         <v>141</v>
       </c>
       <c r="N41" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="O41" t="s">
         <v>9</v>
@@ -2855,93 +2845,93 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D42">
         <v>2861827737</v>
       </c>
       <c r="E42" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G42">
-        <v>25</v>
-      </c>
-      <c r="H42" s="2">
-        <v>5</v>
-      </c>
-      <c r="I42">
-        <v>2</v>
-      </c>
-      <c r="J42">
-        <v>1</v>
-      </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
-      <c r="L42">
-        <v>34</v>
-      </c>
-      <c r="M42">
-        <v>141</v>
+        <v>42</v>
+      </c>
+      <c r="G42" t="s">
+        <v>42</v>
+      </c>
+      <c r="H42" t="s">
+        <v>42</v>
+      </c>
+      <c r="I42" t="s">
+        <v>42</v>
+      </c>
+      <c r="J42" t="s">
+        <v>42</v>
+      </c>
+      <c r="K42" t="s">
+        <v>42</v>
+      </c>
+      <c r="L42" t="s">
+        <v>42</v>
+      </c>
+      <c r="M42" t="s">
+        <v>42</v>
       </c>
       <c r="N42" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="O42" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D43">
         <v>2035806901</v>
       </c>
       <c r="E43" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O43" t="s">
         <v>11</v>
@@ -2949,19 +2939,19 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D44">
         <v>2385333737</v>
       </c>
       <c r="E44" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F44" t="s">
         <v>7</v>
@@ -2969,8 +2959,8 @@
       <c r="G44">
         <v>100</v>
       </c>
-      <c r="H44">
-        <v>4.9000000000000004</v>
+      <c r="H44" t="s">
+        <v>10</v>
       </c>
       <c r="I44">
         <v>13</v>
@@ -2988,7 +2978,7 @@
         <v>141</v>
       </c>
       <c r="N44" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O44" t="s">
         <v>9</v>
@@ -2996,66 +2986,66 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D45">
         <v>4784239772</v>
       </c>
       <c r="E45" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F45" t="s">
-        <v>43</v>
-      </c>
-      <c r="G45" t="s">
-        <v>43</v>
+        <v>7</v>
+      </c>
+      <c r="G45">
+        <v>5</v>
       </c>
       <c r="H45" t="s">
-        <v>43</v>
-      </c>
-      <c r="I45" t="s">
-        <v>43</v>
-      </c>
-      <c r="J45" t="s">
-        <v>43</v>
-      </c>
-      <c r="K45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L45" t="s">
-        <v>43</v>
-      </c>
-      <c r="M45" t="s">
-        <v>43</v>
+        <v>12</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>38</v>
+      </c>
+      <c r="M45">
+        <v>141</v>
       </c>
       <c r="N45" t="s">
-        <v>43</v>
+        <v>160</v>
       </c>
       <c r="O45" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D46">
         <v>5164338894</v>
       </c>
       <c r="E46" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F46" t="s">
         <v>7</v>
@@ -3064,10 +3054,10 @@
         <v>25</v>
       </c>
       <c r="H46" t="s">
-        <v>43</v>
-      </c>
-      <c r="I46" t="s">
-        <v>43</v>
+        <v>12</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
       </c>
       <c r="J46">
         <v>5</v>
@@ -3082,7 +3072,7 @@
         <v>141</v>
       </c>
       <c r="N46" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O46" t="s">
         <v>9</v>
@@ -3090,19 +3080,19 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D47">
         <v>2981481597</v>
       </c>
       <c r="E47" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F47" t="s">
         <v>7</v>
@@ -3129,7 +3119,7 @@
         <v>796</v>
       </c>
       <c r="N47" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="O47" t="s">
         <v>9</v>
@@ -3137,46 +3127,46 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D48">
         <v>1485178523</v>
       </c>
       <c r="E48" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F48" t="s">
-        <v>43</v>
-      </c>
-      <c r="G48" t="s">
-        <v>43</v>
+        <v>49</v>
+      </c>
+      <c r="G48">
+        <v>4</v>
       </c>
       <c r="H48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I48" t="s">
-        <v>43</v>
-      </c>
-      <c r="J48" t="s">
-        <v>43</v>
-      </c>
-      <c r="K48" t="s">
-        <v>43</v>
-      </c>
-      <c r="L48" t="s">
-        <v>43</v>
-      </c>
-      <c r="M48" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="J48">
+        <v>4</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>58</v>
+      </c>
+      <c r="M48">
+        <v>141</v>
       </c>
       <c r="N48" t="s">
-        <v>43</v>
+        <v>161</v>
       </c>
       <c r="O48" t="s">
         <v>11</v>
@@ -3184,46 +3174,46 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D49">
         <v>2742594909</v>
       </c>
       <c r="E49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O49" t="s">
         <v>11</v>
@@ -3231,46 +3221,46 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D50">
         <v>1386149008</v>
       </c>
       <c r="E50" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O50" t="s">
         <v>11</v>
@@ -3278,22 +3268,22 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D51">
         <v>3537814136</v>
       </c>
       <c r="E51" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F51" t="s">
-        <v>7</v>
+        <v>150</v>
       </c>
       <c r="G51">
         <v>1000</v>
@@ -3302,7 +3292,7 @@
         <v>10</v>
       </c>
       <c r="I51">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="J51">
         <v>6</v>
@@ -3317,7 +3307,7 @@
         <v>712</v>
       </c>
       <c r="N51" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="O51" t="s">
         <v>9</v>
@@ -3325,19 +3315,19 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="D52">
         <v>1386166955</v>
       </c>
       <c r="E52" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F52" t="s">
         <v>7</v>
@@ -3346,10 +3336,10 @@
         <v>5000</v>
       </c>
       <c r="H52" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I52">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J52">
         <v>3</v>
@@ -3364,7 +3354,7 @@
         <v>1134</v>
       </c>
       <c r="N52" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="O52" t="s">
         <v>9</v>
@@ -3372,19 +3362,19 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D53">
         <v>3537839838</v>
       </c>
       <c r="E53" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F53" t="s">
         <v>7</v>
@@ -3396,7 +3386,7 @@
         <v>10</v>
       </c>
       <c r="I53">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="J53">
         <v>6</v>
@@ -3411,7 +3401,7 @@
         <v>709</v>
       </c>
       <c r="N53" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="O53" t="s">
         <v>9</v>
@@ -3419,187 +3409,187 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D54">
         <v>3537826888</v>
       </c>
       <c r="E54" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F54" t="s">
-        <v>7</v>
-      </c>
-      <c r="G54">
-        <v>1000</v>
+        <v>42</v>
+      </c>
+      <c r="G54" t="s">
+        <v>42</v>
       </c>
       <c r="H54" t="s">
-        <v>12</v>
-      </c>
-      <c r="I54">
-        <v>6</v>
-      </c>
-      <c r="J54">
-        <v>4</v>
-      </c>
-      <c r="K54">
-        <v>0</v>
-      </c>
-      <c r="L54">
-        <v>54</v>
-      </c>
-      <c r="M54">
-        <v>705</v>
+        <v>42</v>
+      </c>
+      <c r="I54" t="s">
+        <v>42</v>
+      </c>
+      <c r="J54" t="s">
+        <v>42</v>
+      </c>
+      <c r="K54" t="s">
+        <v>42</v>
+      </c>
+      <c r="L54" t="s">
+        <v>42</v>
+      </c>
+      <c r="M54" t="s">
+        <v>42</v>
       </c>
       <c r="N54" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="O54" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D55">
         <v>1344836181</v>
       </c>
       <c r="E55" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F55" t="s">
-        <v>7</v>
-      </c>
-      <c r="G55">
-        <v>1000</v>
+        <v>42</v>
+      </c>
+      <c r="G55" t="s">
+        <v>42</v>
       </c>
       <c r="H55" t="s">
-        <v>8</v>
-      </c>
-      <c r="I55">
-        <v>63</v>
-      </c>
-      <c r="J55">
-        <v>6</v>
-      </c>
-      <c r="K55">
-        <v>0</v>
-      </c>
-      <c r="L55">
-        <v>59</v>
-      </c>
-      <c r="M55">
-        <v>552</v>
+        <v>42</v>
+      </c>
+      <c r="I55" t="s">
+        <v>42</v>
+      </c>
+      <c r="J55" t="s">
+        <v>42</v>
+      </c>
+      <c r="K55" t="s">
+        <v>42</v>
+      </c>
+      <c r="L55" t="s">
+        <v>42</v>
+      </c>
+      <c r="M55" t="s">
+        <v>42</v>
       </c>
       <c r="N55" t="s">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="O55" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="D56">
         <v>1485178537</v>
       </c>
       <c r="E56" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F56" t="s">
-        <v>7</v>
-      </c>
-      <c r="G56">
-        <v>1000</v>
+        <v>42</v>
+      </c>
+      <c r="G56" t="s">
+        <v>42</v>
       </c>
       <c r="H56" t="s">
-        <v>10</v>
-      </c>
-      <c r="I56">
-        <v>97</v>
-      </c>
-      <c r="J56">
-        <v>6</v>
-      </c>
-      <c r="K56">
-        <v>0</v>
-      </c>
-      <c r="L56">
-        <v>56</v>
-      </c>
-      <c r="M56">
-        <v>551</v>
+        <v>42</v>
+      </c>
+      <c r="I56" t="s">
+        <v>42</v>
+      </c>
+      <c r="J56" t="s">
+        <v>42</v>
+      </c>
+      <c r="K56" t="s">
+        <v>42</v>
+      </c>
+      <c r="L56" t="s">
+        <v>42</v>
+      </c>
+      <c r="M56" t="s">
+        <v>42</v>
       </c>
       <c r="N56" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="O56" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D57">
         <v>3537738384</v>
       </c>
       <c r="E57" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O57" t="s">
         <v>11</v>
@@ -3607,19 +3597,19 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="D58">
         <v>5507380358</v>
       </c>
       <c r="E58" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F58" t="s">
         <v>7</v>
@@ -3628,10 +3618,10 @@
         <v>500</v>
       </c>
       <c r="H58" t="s">
-        <v>43</v>
-      </c>
-      <c r="I58" t="s">
-        <v>43</v>
+        <v>12</v>
+      </c>
+      <c r="I58">
+        <v>15</v>
       </c>
       <c r="J58">
         <v>5</v>
@@ -3640,13 +3630,13 @@
         <v>0</v>
       </c>
       <c r="L58">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="M58">
         <v>923</v>
       </c>
       <c r="N58" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O58" t="s">
         <v>9</v>
@@ -3654,19 +3644,19 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D59">
         <v>1485123308</v>
       </c>
       <c r="E59" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F59" t="s">
         <v>7</v>
@@ -3678,7 +3668,7 @@
         <v>10</v>
       </c>
       <c r="I59">
-        <v>13045</v>
+        <v>14866</v>
       </c>
       <c r="J59">
         <v>6</v>
@@ -3693,7 +3683,7 @@
         <v>734</v>
       </c>
       <c r="N59" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="O59" t="s">
         <v>9</v>
@@ -3701,19 +3691,19 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D60">
         <v>2035712373</v>
       </c>
       <c r="E60" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F60" t="s">
         <v>7</v>
@@ -3722,10 +3712,10 @@
         <v>1000</v>
       </c>
       <c r="H60" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I60">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="J60">
         <v>2</v>
@@ -3740,7 +3730,7 @@
         <v>735</v>
       </c>
       <c r="N60" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="O60" t="s">
         <v>9</v>
@@ -3748,46 +3738,46 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D61">
         <v>2739131393</v>
       </c>
       <c r="E61" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O61" t="s">
         <v>11</v>
@@ -3795,46 +3785,46 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D62">
         <v>1485148997</v>
       </c>
       <c r="E62" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F62" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G62" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H62" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I62" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J62" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K62" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L62" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M62" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N62" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O62" t="s">
         <v>11</v>
@@ -3842,46 +3832,46 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D63">
         <v>2372468289</v>
       </c>
       <c r="E63" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F63" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G63" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H63" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I63" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J63" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K63" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L63" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M63" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N63" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O63" t="s">
         <v>11</v>
@@ -3889,46 +3879,46 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D64">
         <v>1918665431</v>
       </c>
       <c r="E64" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F64" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G64" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H64" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I64" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J64" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K64" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L64" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M64" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N64" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O64" t="s">
         <v>11</v>
@@ -3936,46 +3926,46 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D65">
         <v>1918627059</v>
       </c>
       <c r="E65" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O65" t="s">
         <v>11</v>
@@ -3983,46 +3973,46 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D66">
         <v>1918627057</v>
       </c>
       <c r="E66" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O66" t="s">
         <v>11</v>
@@ -4030,66 +4020,66 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="D67">
         <v>2035768243</v>
       </c>
       <c r="E67" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F67" t="s">
-        <v>7</v>
-      </c>
-      <c r="G67">
-        <v>1000</v>
+        <v>42</v>
+      </c>
+      <c r="G67" t="s">
+        <v>42</v>
       </c>
       <c r="H67" t="s">
-        <v>120</v>
-      </c>
-      <c r="I67">
-        <v>7</v>
-      </c>
-      <c r="J67">
-        <v>3</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="L67">
-        <v>56</v>
-      </c>
-      <c r="M67">
-        <v>292</v>
+        <v>42</v>
+      </c>
+      <c r="I67" t="s">
+        <v>42</v>
+      </c>
+      <c r="J67" t="s">
+        <v>42</v>
+      </c>
+      <c r="K67" t="s">
+        <v>42</v>
+      </c>
+      <c r="L67" t="s">
+        <v>42</v>
+      </c>
+      <c r="M67" t="s">
+        <v>42</v>
       </c>
       <c r="N67" t="s">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="O67" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D68">
         <v>2261248051</v>
       </c>
       <c r="E68" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F68" t="s">
         <v>7</v>
@@ -4101,7 +4091,7 @@
         <v>8</v>
       </c>
       <c r="I68">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J68">
         <v>6</v>
@@ -4116,7 +4106,7 @@
         <v>952</v>
       </c>
       <c r="N68" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="O68" t="s">
         <v>9</v>
@@ -4124,19 +4114,19 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D69">
         <v>3545957692</v>
       </c>
       <c r="E69" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F69" t="s">
         <v>7</v>
@@ -4148,7 +4138,7 @@
         <v>8</v>
       </c>
       <c r="I69">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J69">
         <v>6</v>
@@ -4163,7 +4153,7 @@
         <v>953</v>
       </c>
       <c r="N69" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="O69" t="s">
         <v>9</v>
@@ -4171,19 +4161,19 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D70">
         <v>2261286679</v>
       </c>
       <c r="E70" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F70" t="s">
         <v>7</v>
@@ -4210,7 +4200,7 @@
         <v>1212</v>
       </c>
       <c r="N70" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="O70" t="s">
         <v>9</v>
@@ -4218,46 +4208,46 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D71">
         <v>2261467877</v>
       </c>
       <c r="E71" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F71" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G71" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H71" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I71" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J71" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K71" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L71" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M71" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N71" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O71" t="s">
         <v>11</v>
@@ -4265,19 +4255,19 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D72">
         <v>2261261115</v>
       </c>
       <c r="E72" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F72" t="s">
         <v>7</v>
@@ -4304,7 +4294,7 @@
         <v>1156</v>
       </c>
       <c r="N72" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="O72" t="s">
         <v>9</v>
@@ -4312,22 +4302,22 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D73">
         <v>2261338395</v>
       </c>
       <c r="E73" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F73" t="s">
-        <v>131</v>
+        <v>7</v>
       </c>
       <c r="G73">
         <v>10000</v>
@@ -4336,7 +4326,7 @@
         <v>10</v>
       </c>
       <c r="I73">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="J73">
         <v>6</v>
@@ -4351,7 +4341,7 @@
         <v>789</v>
       </c>
       <c r="N73" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="O73" t="s">
         <v>11</v>
@@ -4359,66 +4349,66 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="D74">
         <v>2261442019</v>
       </c>
       <c r="E74" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F74" t="s">
-        <v>7</v>
-      </c>
-      <c r="G74">
-        <v>1000</v>
+        <v>42</v>
+      </c>
+      <c r="G74" t="s">
+        <v>42</v>
       </c>
       <c r="H74" t="s">
-        <v>10</v>
-      </c>
-      <c r="I74">
-        <v>70</v>
-      </c>
-      <c r="J74">
-        <v>4</v>
-      </c>
-      <c r="K74">
-        <v>0</v>
-      </c>
-      <c r="L74">
-        <v>60</v>
-      </c>
-      <c r="M74">
-        <v>461</v>
+        <v>42</v>
+      </c>
+      <c r="I74" t="s">
+        <v>42</v>
+      </c>
+      <c r="J74" t="s">
+        <v>42</v>
+      </c>
+      <c r="K74" t="s">
+        <v>42</v>
+      </c>
+      <c r="L74" t="s">
+        <v>42</v>
+      </c>
+      <c r="M74" t="s">
+        <v>42</v>
       </c>
       <c r="N74" t="s">
-        <v>135</v>
+        <v>42</v>
       </c>
       <c r="O74" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="D75">
         <v>3537826900</v>
       </c>
       <c r="E75" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F75" t="s">
         <v>7</v>
@@ -4430,7 +4420,7 @@
         <v>12</v>
       </c>
       <c r="I75">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J75">
         <v>6</v>
@@ -4445,7 +4435,7 @@
         <v>1002</v>
       </c>
       <c r="N75" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="O75" t="s">
         <v>9</v>
@@ -4453,22 +4443,22 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D76">
         <v>2662179544</v>
       </c>
       <c r="E76" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F76" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G76">
         <v>5000</v>
@@ -4477,7 +4467,7 @@
         <v>10</v>
       </c>
       <c r="I76">
-        <v>3220</v>
+        <v>2363</v>
       </c>
       <c r="J76">
         <v>4</v>
@@ -4492,7 +4482,7 @@
         <v>660</v>
       </c>
       <c r="N76" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O76" t="s">
         <v>11</v>
@@ -4500,22 +4490,22 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D77">
         <v>1975274217</v>
       </c>
       <c r="E77" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F77" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G77">
         <v>10000</v>
@@ -4524,7 +4514,7 @@
         <v>10</v>
       </c>
       <c r="I77">
-        <v>3220</v>
+        <v>3100</v>
       </c>
       <c r="J77">
         <v>4</v>
@@ -4539,7 +4529,7 @@
         <v>600</v>
       </c>
       <c r="N77" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O77" t="s">
         <v>11</v>
@@ -4547,46 +4537,46 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D78">
         <v>2264056624</v>
       </c>
       <c r="E78" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F78" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G78" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H78" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I78" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J78" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K78" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L78" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M78" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N78" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O78" t="s">
         <v>11</v>
@@ -4594,96 +4584,96 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D79">
         <v>4783958938</v>
       </c>
       <c r="E79" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F79" t="s">
-        <v>43</v>
-      </c>
-      <c r="G79" t="s">
-        <v>43</v>
+        <v>7</v>
+      </c>
+      <c r="G79">
+        <v>25</v>
       </c>
       <c r="H79" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I79" t="s">
-        <v>43</v>
-      </c>
-      <c r="J79" t="s">
-        <v>43</v>
-      </c>
-      <c r="K79" t="s">
-        <v>43</v>
-      </c>
-      <c r="L79" t="s">
-        <v>43</v>
-      </c>
-      <c r="M79" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="J79">
+        <v>5</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>44</v>
+      </c>
+      <c r="M79">
+        <v>141</v>
       </c>
       <c r="N79" t="s">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="O79" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D80">
         <v>5158476730</v>
       </c>
       <c r="E80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F80" t="s">
-        <v>43</v>
-      </c>
-      <c r="G80" t="s">
-        <v>43</v>
+        <v>7</v>
+      </c>
+      <c r="G80">
+        <v>25</v>
       </c>
       <c r="H80" t="s">
-        <v>43</v>
-      </c>
-      <c r="I80" t="s">
-        <v>43</v>
-      </c>
-      <c r="J80" t="s">
-        <v>43</v>
-      </c>
-      <c r="K80" t="s">
-        <v>43</v>
-      </c>
-      <c r="L80" t="s">
-        <v>43</v>
-      </c>
-      <c r="M80" t="s">
-        <v>43</v>
+        <v>12</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+      <c r="J80">
+        <v>4</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>45</v>
+      </c>
+      <c r="M80">
+        <v>141</v>
       </c>
       <c r="N80" t="s">
-        <v>43</v>
+        <v>164</v>
       </c>
       <c r="O80" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
